--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_2.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_2_2.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="8820"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表2-2除回购和拆借外贷款按行业、企业" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -39,9 +44,6 @@
   </si>
   <si>
     <t>产品品种：</t>
-  </si>
-  <si>
-    <t>单位：万元</t>
   </si>
   <si>
     <t>列编号</t>
@@ -603,6 +605,8 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
       </rPr>
       <t>境内个人</t>
     </r>
@@ -668,6 +672,10 @@
   </si>
   <si>
     <t>${report.enddate}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -690,23 +698,27 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -719,11 +731,13 @@
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -735,6 +749,7 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -746,6 +761,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -968,9 +984,6 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -980,21 +993,27 @@
     <xf numFmtId="180" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1002,9 +1021,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1028,6 +1044,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1376,7 +1395,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1398,17 +1417,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1">
       <c r="A2" s="2"/>
@@ -1418,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="2"/>
@@ -1429,702 +1448,702 @@
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C3" s="49"/>
+      <c r="B3" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="47"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="49" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="49"/>
+      <c r="E3" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="47"/>
       <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="I3" s="50"/>
+      <c r="H3" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="1:9" s="10" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="51"/>
+      <c r="B4" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="52"/>
       <c r="D4" s="37"/>
       <c r="E4" s="38"/>
       <c r="F4" s="38"/>
       <c r="G4" s="39"/>
       <c r="H4" s="40"/>
-      <c r="I4" s="41" t="s">
-        <v>6</v>
+      <c r="I4" s="44" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.95" customHeight="1">
       <c r="A5" s="30"/>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="53"/>
+      <c r="D5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="31" t="s">
+      <c r="E5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="F5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="G5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="H5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="34" t="s">
+      <c r="I5" s="35" t="s">
         <v>12</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="14" customFormat="1" ht="31.5" customHeight="1">
       <c r="A6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="C6" s="46"/>
+      <c r="D6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="F6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="H6" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="I6" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="15" customFormat="1" ht="15.95" customHeight="1">
       <c r="A7" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="C7" s="49"/>
+      <c r="D7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="26" t="s">
+      <c r="E7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="G7" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="H7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="I7" s="26" t="s">
         <v>28</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.95" customHeight="1">
       <c r="A8" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="47" t="s">
+      <c r="C8" s="45"/>
+      <c r="D8" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="26" t="s">
+      <c r="E8" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="H8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="I8" s="26" t="s">
         <v>36</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.95" customHeight="1">
       <c r="A9" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="C9" s="45"/>
+      <c r="D9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="26" t="s">
+      <c r="E9" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="F9" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="G9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="H9" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="I9" s="26" t="s">
         <v>44</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1">
       <c r="A10" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="26" t="s">
+      <c r="E10" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="G10" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="H10" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="I10" s="26" t="s">
         <v>52</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.95" customHeight="1">
       <c r="A11" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="26" t="s">
+      <c r="E11" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="F11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="G11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="H11" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="I11" s="26" t="s">
         <v>60</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1">
       <c r="A12" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="47" t="s">
+      <c r="C12" s="45"/>
+      <c r="D12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="47"/>
-      <c r="D12" s="26" t="s">
+      <c r="E12" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="F12" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="G12" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="H12" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="I12" s="26" t="s">
         <v>68</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1">
       <c r="A13" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="26" t="s">
+      <c r="E13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="G13" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="H13" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="I13" s="26" t="s">
         <v>76</v>
-      </c>
-      <c r="I13" s="26" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1">
       <c r="A14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="47" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="26" t="s">
+      <c r="E14" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="F14" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="G14" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="H14" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="I14" s="26" t="s">
         <v>84</v>
-      </c>
-      <c r="I14" s="26" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1">
       <c r="A15" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="C15" s="45"/>
+      <c r="D15" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="26" t="s">
+      <c r="E15" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="F15" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="G15" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="H15" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="I15" s="26" t="s">
         <v>92</v>
-      </c>
-      <c r="I15" s="26" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1">
       <c r="A16" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="C16" s="45"/>
+      <c r="D16" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="26" t="s">
+      <c r="E16" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="F16" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="H16" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="I16" s="26" t="s">
         <v>100</v>
-      </c>
-      <c r="I16" s="26" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.95" customHeight="1">
       <c r="A17" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="26" t="s">
+      <c r="E17" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="F17" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="26" t="s">
+      <c r="G17" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="H17" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="I17" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="I17" s="26" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.95" customHeight="1">
       <c r="A18" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="47" t="s">
+      <c r="C18" s="45"/>
+      <c r="D18" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="26" t="s">
+      <c r="E18" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="F18" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="26" t="s">
+      <c r="G18" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="H18" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="I18" s="26" t="s">
         <v>116</v>
-      </c>
-      <c r="I18" s="26" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1">
       <c r="A19" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="C19" s="45"/>
+      <c r="D19" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="26" t="s">
+      <c r="E19" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="F19" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="F19" s="26" t="s">
+      <c r="G19" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="H19" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="H19" s="26" t="s">
+      <c r="I19" s="26" t="s">
         <v>124</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1">
       <c r="A20" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="26" t="s">
+      <c r="E20" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="F20" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="G20" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="H20" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="H20" s="26" t="s">
+      <c r="I20" s="26" t="s">
         <v>132</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1">
       <c r="A21" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="C21" s="45"/>
+      <c r="D21" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="26" t="s">
+      <c r="E21" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="F21" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="G21" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="H21" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="H21" s="26" t="s">
+      <c r="I21" s="26" t="s">
         <v>140</v>
-      </c>
-      <c r="I21" s="26" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1">
       <c r="A22" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="C22" s="45"/>
+      <c r="D22" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="26" t="s">
+      <c r="E22" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="F22" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="G22" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="H22" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="H22" s="26" t="s">
+      <c r="I22" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="I22" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.95" customHeight="1">
       <c r="A23" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="C23" s="45"/>
+      <c r="D23" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="26" t="s">
+      <c r="E23" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="F23" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="G23" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="H23" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="I23" s="26" t="s">
         <v>156</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.95" customHeight="1">
       <c r="A24" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="C24" s="45"/>
+      <c r="D24" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="26" t="s">
+      <c r="E24" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="F24" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="G24" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="G24" s="26" t="s">
+      <c r="H24" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="26" t="s">
+      <c r="I24" s="26" t="s">
         <v>164</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1">
       <c r="A25" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="C25" s="45"/>
+      <c r="D25" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="26" t="s">
+      <c r="E25" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="F25" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="G25" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="H25" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="H25" s="26" t="s">
+      <c r="I25" s="26" t="s">
         <v>172</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.95" customHeight="1">
       <c r="A26" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="B26" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="C26" s="45"/>
+      <c r="D26" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="26" t="s">
+      <c r="E26" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="F26" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="G26" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="H26" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="H26" s="26" t="s">
+      <c r="I26" s="26" t="s">
         <v>180</v>
-      </c>
-      <c r="I26" s="26" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1">
       <c r="A27" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="C27" s="45"/>
+      <c r="D27" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="26" t="s">
+      <c r="E27" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="G27" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="H27" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="I27" s="26" t="s">
         <v>188</v>
-      </c>
-      <c r="I27" s="26" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1">
       <c r="A28" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="B28" s="55" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="47"/>
+      <c r="C28" s="45"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
       <c r="H28" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="I28" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="I28" s="26" t="s">
+    </row>
+    <row r="29" spans="1:9" ht="15.95" customHeight="1" thickBot="1">
+      <c r="A29" s="41" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.95" customHeight="1" thickBot="1">
-      <c r="A29" s="42" t="s">
+      <c r="B29" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="C29" s="56"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44" t="s">
+      <c r="I29" s="43" t="s">
         <v>196</v>
-      </c>
-      <c r="I29" s="44" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="74.25" customHeight="1">
       <c r="A30" s="54" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B30" s="54"/>
       <c r="C30" s="54"/>
@@ -2137,25 +2156,25 @@
     </row>
     <row r="31" spans="1:9" s="21" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F31" s="17"/>
       <c r="G31" s="20"/>
       <c r="H31" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2181,20 +2200,20 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="2">
